--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_4.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01760222338763584</v>
+        <v>0.01145233460325144</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008431490956486723</v>
+        <v>0.008423128287666226</v>
       </c>
       <c r="C2" t="n">
-        <v>25185108</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25185108</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>18165772</v>
+        <v>4453022</v>
       </c>
       <c r="L2" t="n">
-        <v>10536908</v>
+        <v>2539349</v>
       </c>
       <c r="M2" t="n">
-        <v>2670265</v>
+        <v>617753</v>
       </c>
       <c r="N2" t="n">
-        <v>138221</v>
+        <v>29789</v>
       </c>
       <c r="O2" t="n">
-        <v>1615643</v>
+        <v>381958</v>
       </c>
       <c r="P2" t="n">
-        <v>645075</v>
+        <v>155499</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999834299087524</v>
+        <v>0.9999990463256836</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9031792879104614</v>
+        <v>0.8848015069961548</v>
       </c>
       <c r="S2" t="n">
-        <v>0.799784243106842</v>
+        <v>0.7599801421165466</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7401212453842163</v>
+        <v>0.70171058177948</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5236595869064331</v>
+        <v>0.4365904033184052</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7901923060417175</v>
+        <v>0.7552666664123535</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8535018563270569</v>
+        <v>0.8263399600982666</v>
       </c>
       <c r="X2" t="n">
-        <v>25185108</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,314 +742,314 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25185108</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>19203868</v>
+        <v>4809709</v>
       </c>
       <c r="AG2" t="n">
-        <v>11844967</v>
+        <v>2974674</v>
       </c>
       <c r="AH2" t="n">
-        <v>3194227</v>
+        <v>799643</v>
       </c>
       <c r="AI2" t="n">
-        <v>235673</v>
+        <v>59000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1835708</v>
+        <v>459265</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565847516059875</v>
+        <v>0.956451416015625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911228358745575</v>
+        <v>0.9113048315048218</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.85814368724823</v>
+        <v>0.8578755855560303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624941229820251</v>
+        <v>0.6619618535041809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020473957061768</v>
+        <v>0.9019733667373657</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.004257999283037396</v>
+        <v>0.002702361791632925</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002022527131276332</v>
+        <v>0.002019936826367219</v>
       </c>
       <c r="C3" t="n">
-        <v>363</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>18165772</v>
+        <v>4453022</v>
       </c>
       <c r="E3" t="n">
-        <v>1844740</v>
+        <v>561444</v>
       </c>
       <c r="F3" t="n">
-        <v>37534</v>
+        <v>7503</v>
       </c>
       <c r="G3" t="n">
-        <v>4685</v>
+        <v>861</v>
       </c>
       <c r="H3" t="n">
-        <v>1770</v>
+        <v>376</v>
       </c>
       <c r="I3" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>39960074</v>
+        <v>10016616</v>
       </c>
       <c r="K3" t="n">
-        <v>43143283</v>
+        <v>10726601</v>
       </c>
       <c r="L3" t="n">
-        <v>49491663</v>
+        <v>12258726</v>
       </c>
       <c r="M3" t="n">
-        <v>60483757</v>
+        <v>15134409</v>
       </c>
       <c r="N3" t="n">
-        <v>64663846</v>
+        <v>16201967</v>
       </c>
       <c r="O3" t="n">
-        <v>62680684</v>
+        <v>15696454</v>
       </c>
       <c r="P3" t="n">
-        <v>64261685</v>
+        <v>16103575</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9057999849319458</v>
+        <v>0.8864859342575073</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8095252513885498</v>
+        <v>0.7768237590789795</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7169973254203796</v>
+        <v>0.6624050736427307</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3882361650466919</v>
+        <v>0.3339911103248596</v>
       </c>
       <c r="V3" t="n">
-        <v>0.793561577796936</v>
+        <v>0.7498517632484436</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8343011736869812</v>
+        <v>0.8042525053024292</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19203868</v>
+        <v>4809709</v>
       </c>
       <c r="Z3" t="n">
-        <v>789624</v>
+        <v>198076</v>
       </c>
       <c r="AA3" t="n">
-        <v>34065</v>
+        <v>8559</v>
       </c>
       <c r="AB3" t="n">
-        <v>27091</v>
+        <v>6810</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>39960492</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>44219072</v>
+        <v>11087378</v>
       </c>
       <c r="AG3" t="n">
-        <v>50975509</v>
+        <v>12771195</v>
       </c>
       <c r="AH3" t="n">
-        <v>60893342</v>
+        <v>15264532</v>
       </c>
       <c r="AI3" t="n">
-        <v>64669514</v>
+        <v>16210280</v>
       </c>
       <c r="AJ3" t="n">
-        <v>62910323</v>
+        <v>15770309</v>
       </c>
       <c r="AK3" t="n">
-        <v>64319392</v>
+        <v>16123000</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575625658035278</v>
+        <v>0.9574934840202332</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100202918052673</v>
+        <v>0.909995973110199</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85768723487854</v>
+        <v>0.857442319393158</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6619600653648376</v>
+        <v>0.6615017056465149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016517400741577</v>
+        <v>0.9016192555427551</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04960695307988913</v>
+        <v>0.03579494038944363</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03190658617682631</v>
+        <v>0.0318805782860274</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1845415</v>
+        <v>550268</v>
       </c>
       <c r="E4" t="n">
-        <v>10536908</v>
+        <v>2539349</v>
       </c>
       <c r="F4" t="n">
-        <v>574340</v>
+        <v>161062</v>
       </c>
       <c r="G4" t="n">
-        <v>16604</v>
+        <v>5201</v>
       </c>
       <c r="H4" t="n">
-        <v>39714</v>
+        <v>12072</v>
       </c>
       <c r="I4" t="n">
-        <v>3176</v>
+        <v>935</v>
       </c>
       <c r="J4" t="n">
-        <v>418</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>1947369</v>
+        <v>579770</v>
       </c>
       <c r="L4" t="n">
-        <v>2637780</v>
+        <v>801987</v>
       </c>
       <c r="M4" t="n">
-        <v>937610</v>
+        <v>262600</v>
       </c>
       <c r="N4" t="n">
-        <v>125731</v>
+        <v>38442</v>
       </c>
       <c r="O4" t="n">
-        <v>428977</v>
+        <v>123768</v>
       </c>
       <c r="P4" t="n">
-        <v>110723</v>
+        <v>32679</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999917149543762</v>
+        <v>0.9999995231628418</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9044877290725708</v>
+        <v>0.885642945766449</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8046253323554993</v>
+        <v>0.7683096528053284</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7283758521080017</v>
+        <v>0.6814915537834167</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4458921849727631</v>
+        <v>0.3784604668617249</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7918733954429626</v>
+        <v>0.7525495290756226</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8437923192977905</v>
+        <v>0.8151466846466064</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>813684</v>
+        <v>204447</v>
       </c>
       <c r="Z4" t="n">
-        <v>11844967</v>
+        <v>2974674</v>
       </c>
       <c r="AA4" t="n">
-        <v>330759</v>
+        <v>83051</v>
       </c>
       <c r="AB4" t="n">
-        <v>21895</v>
+        <v>5499</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>871580</v>
+        <v>218993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1153934</v>
+        <v>289518</v>
       </c>
       <c r="AH4" t="n">
-        <v>528025</v>
+        <v>132477</v>
       </c>
       <c r="AI4" t="n">
-        <v>120063</v>
+        <v>30129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199338</v>
+        <v>49913</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570733904838562</v>
+        <v>0.9569721221923828</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106239080429077</v>
+        <v>0.9106499552726746</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579154014587402</v>
+        <v>0.857658863067627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622269749641418</v>
+        <v>0.6617317199707031</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018495678901672</v>
+        <v>0.9017962217330933</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>62355</v>
+        <v>18068</v>
       </c>
       <c r="E5" t="n">
-        <v>688583</v>
+        <v>208353</v>
       </c>
       <c r="F5" t="n">
-        <v>2670265</v>
+        <v>617753</v>
       </c>
       <c r="G5" t="n">
-        <v>56152</v>
+        <v>16492</v>
       </c>
       <c r="H5" t="n">
-        <v>231206</v>
+        <v>67041</v>
       </c>
       <c r="I5" t="n">
-        <v>15672</v>
+        <v>4884</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1889176</v>
+        <v>570207</v>
       </c>
       <c r="L5" t="n">
-        <v>2479249</v>
+        <v>729538</v>
       </c>
       <c r="M5" t="n">
-        <v>1053968</v>
+        <v>314838</v>
       </c>
       <c r="N5" t="n">
-        <v>217802</v>
+        <v>59402</v>
       </c>
       <c r="O5" t="n">
-        <v>420296</v>
+        <v>127420</v>
       </c>
       <c r="P5" t="n">
-        <v>128117</v>
+        <v>37847</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999935626983643</v>
+        <v>0.9999996423721313</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9411081671714783</v>
+        <v>0.9295771718025208</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9214524030685425</v>
+        <v>0.9062117338180542</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9694288372993469</v>
+        <v>0.9646385908126831</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9947267174720764</v>
+        <v>0.9940081834793091</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9869634509086609</v>
+        <v>0.9846176505088806</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9963337779045105</v>
+        <v>0.99568110704422</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>31947</v>
+        <v>8028</v>
       </c>
       <c r="Z5" t="n">
-        <v>339404</v>
+        <v>85185</v>
       </c>
       <c r="AA5" t="n">
-        <v>3194227</v>
+        <v>799643</v>
       </c>
       <c r="AB5" t="n">
-        <v>39720</v>
+        <v>9960</v>
       </c>
       <c r="AC5" t="n">
-        <v>116403</v>
+        <v>29142</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>851080</v>
+        <v>213520</v>
       </c>
       <c r="AG5" t="n">
-        <v>1171190</v>
+        <v>294213</v>
       </c>
       <c r="AH5" t="n">
-        <v>530006</v>
+        <v>132948</v>
       </c>
       <c r="AI5" t="n">
-        <v>120350</v>
+        <v>30191</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200231</v>
+        <v>50113</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735567569732666</v>
+        <v>0.9735135436058044</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643087983131409</v>
+        <v>0.9642531871795654</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837589859962463</v>
+        <v>0.9837457537651062</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963095784187317</v>
+        <v>0.9963061213493347</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993866503238678</v>
+        <v>0.9938745498657227</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983711242675781</v>
+        <v>0.9983739256858826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>39129</v>
+        <v>11381</v>
       </c>
       <c r="E6" t="n">
-        <v>62090</v>
+        <v>18889</v>
       </c>
       <c r="F6" t="n">
-        <v>71699</v>
+        <v>17647</v>
       </c>
       <c r="G6" t="n">
-        <v>138221</v>
+        <v>29789</v>
       </c>
       <c r="H6" t="n">
-        <v>41160</v>
+        <v>10412</v>
       </c>
       <c r="I6" t="n">
-        <v>3697</v>
+        <v>1072</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25726</v>
+        <v>6462</v>
       </c>
       <c r="Z6" t="n">
-        <v>21345</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>43462</v>
+        <v>10898</v>
       </c>
       <c r="AB6" t="n">
-        <v>235673</v>
+        <v>59000</v>
       </c>
       <c r="AC6" t="n">
-        <v>27893</v>
+        <v>6984</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>382</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>40310</v>
+        <v>12697</v>
       </c>
       <c r="F7" t="n">
-        <v>245813</v>
+        <v>73859</v>
       </c>
       <c r="G7" t="n">
-        <v>45697</v>
+        <v>15077</v>
       </c>
       <c r="H7" t="n">
-        <v>1615643</v>
+        <v>381958</v>
       </c>
       <c r="I7" t="n">
-        <v>88094</v>
+        <v>25765</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3237</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118419</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30296</v>
+        <v>7594</v>
       </c>
       <c r="AC7" t="n">
-        <v>1835708</v>
+        <v>459265</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>2057</v>
+        <v>604</v>
       </c>
       <c r="F8" t="n">
-        <v>8224</v>
+        <v>2529</v>
       </c>
       <c r="G8" t="n">
-        <v>2593</v>
+        <v>811</v>
       </c>
       <c r="H8" t="n">
-        <v>115127</v>
+        <v>33867</v>
       </c>
       <c r="I8" t="n">
-        <v>645075</v>
+        <v>155499</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
